--- a/variable_selection/spearman_corr.xlsx
+++ b/variable_selection/spearman_corr.xlsx
@@ -633,16 +633,16 @@
         <v>0.05464784851384367</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01151015823584118</v>
+        <v>-0.008582926183503484</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01319602701042989</v>
+        <v>-0.009418036667860282</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09471263459993598</v>
+        <v>-0.08393553397886809</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01094279151377623</v>
+        <v>0.01470941782638088</v>
       </c>
       <c r="H2" t="n">
         <v>0.214483556064516</v>
@@ -654,10 +654,10 @@
         <v>-0.0831481166809236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0272098233524093</v>
+        <v>0.02746506530380317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04824905490442002</v>
+        <v>0.04879151513855512</v>
       </c>
       <c r="M2" t="n">
         <v>-0.09218186642796126</v>
@@ -666,13 +666,13 @@
         <v>-0.03023355562177829</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1337581119984088</v>
+        <v>-0.1468008025855293</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05841151381732715</v>
+        <v>-0.05540373604059472</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1784129385270832</v>
+        <v>-0.19223126410265</v>
       </c>
       <c r="R2" t="n">
         <v>0.2149625413978098</v>
@@ -690,7 +690,7 @@
         <v>0.1298006995814683</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1345780502869412</v>
+        <v>0.1241478225135855</v>
       </c>
       <c r="X2" t="n">
         <v>0.1053039678963239</v>
@@ -708,7 +708,7 @@
         <v>-0.0001964359694476521</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1438657730990845</v>
+        <v>0.1269846847003911</v>
       </c>
       <c r="AD2" t="n">
         <v>0.0159870076590128</v>
@@ -726,19 +726,19 @@
         <v>-0.1154809729727626</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.09122175390201313</v>
+        <v>-0.08484240742183938</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1627150701953262</v>
+        <v>0.1548307510922242</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.04383903999429569</v>
+        <v>-0.04669591536004186</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01094470101620679</v>
+        <v>0.02271001079786113</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.0244739038608021</v>
+        <v>-0.004955794830383358</v>
       </c>
     </row>
     <row r="3">
@@ -754,16 +754,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03418840889389801</v>
+        <v>-0.03314244009213046</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0003693213973934911</v>
+        <v>-0.004331529456284338</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01895352322346457</v>
+        <v>-0.01173118333885382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07056816740915545</v>
+        <v>0.07730443382765217</v>
       </c>
       <c r="H3" t="n">
         <v>-0.05910584493566232</v>
@@ -775,10 +775,10 @@
         <v>0.1083157273134549</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.06172449749494453</v>
+        <v>-0.06201832835607052</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.03119773000218447</v>
+        <v>-0.01660318925918855</v>
       </c>
       <c r="M3" t="n">
         <v>-0.0823706935463982</v>
@@ -787,13 +787,13 @@
         <v>-0.1487514601245411</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03503520605230256</v>
+        <v>0.008059420081243192</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1550102215298965</v>
+        <v>-0.1415285512189099</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1898946962036527</v>
+        <v>0.1384407829480833</v>
       </c>
       <c r="R3" t="n">
         <v>-0.1274492471065007</v>
@@ -811,7 +811,7 @@
         <v>-0.122279895129924</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.03850370537400002</v>
+        <v>-0.06186766340192854</v>
       </c>
       <c r="X3" t="n">
         <v>-0.06837081063659178</v>
@@ -829,7 +829,7 @@
         <v>-0.03729635175521668</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1098479626493104</v>
+        <v>0.09346809140231702</v>
       </c>
       <c r="AD3" t="n">
         <v>-0.05659509016403137</v>
@@ -847,19 +847,19 @@
         <v>-0.1804670030622347</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.06052092828100717</v>
+        <v>-0.06190062399522441</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0625304406048659</v>
+        <v>-0.06246099591702999</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.04933643333490437</v>
+        <v>0.05126529561964581</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01609378458120131</v>
+        <v>0.000350193098988409</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1386092172685593</v>
+        <v>0.1287119571779566</v>
       </c>
     </row>
     <row r="4">
@@ -869,118 +869,118 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.01151015823584118</v>
+        <v>-0.008582926183503484</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.03418840889389801</v>
+        <v>-0.03314244009213046</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0352285163484697</v>
+        <v>-0.03389192302593278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04915779677378923</v>
+        <v>0.04085650046777985</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002903920487998338</v>
+        <v>0.005514093251299968</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07829120642947386</v>
+        <v>0.07795758701857826</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01986544037384717</v>
+        <v>-0.01487887442821797</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03076628385097013</v>
+        <v>0.02961069733445537</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03524486871065791</v>
+        <v>0.03740833441756483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03833246208139141</v>
+        <v>0.03498738793209868</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05048280087593122</v>
+        <v>-0.04876633219291477</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02447886084986306</v>
+        <v>-0.02416072415611886</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.03444272703738956</v>
+        <v>-0.02014874515684935</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01456019065820884</v>
+        <v>-0.01549428869572865</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007387010307146017</v>
+        <v>0.0280904804947647</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02290608424599904</v>
+        <v>0.02444212152457531</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02492493770271854</v>
+        <v>0.02662024472783422</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02584805745305325</v>
+        <v>0.02557863773821953</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.02546250330274214</v>
+        <v>-0.02192240387799482</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.049731060955252</v>
+        <v>-0.04619623319854044</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.04984904678696692</v>
+        <v>-0.03064949227689961</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05865768480797615</v>
+        <v>0.05982479211141413</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02857124055848427</v>
+        <v>0.03009571706568123</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.022952246650036</v>
+        <v>0.02210086423804243</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.0234822200676378</v>
+        <v>-0.02154627495444019</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05274772388314103</v>
+        <v>0.04957843309595</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04497097937068635</v>
+        <v>0.03574659532484323</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.08965074088428525</v>
+        <v>0.08546413368914059</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1031362400804397</v>
+        <v>0.09841387610885519</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0843632097106502</v>
+        <v>0.08007122767994836</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.07362567471653692</v>
+        <v>0.06991747601996672</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.014911793856841</v>
+        <v>-0.02110083653051632</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0681972214148943</v>
+        <v>0.06881470152137929</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01502787558114161</v>
+        <v>0.01378883235348099</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03522436781876354</v>
+        <v>0.03388822699170132</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05060798604217933</v>
+        <v>0.05195175966304226</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.134523572250927</v>
+        <v>-0.13337518964588</v>
       </c>
     </row>
     <row r="5">
@@ -990,118 +990,118 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01319602701042989</v>
+        <v>-0.009418036667860282</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0003693213973934911</v>
+        <v>-0.004331529456284338</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0352285163484697</v>
+        <v>-0.03389192302593278</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.06912092985689866</v>
+        <v>-0.07424450085306426</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01478174307360012</v>
+        <v>0.006023523174550668</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04849656045851726</v>
+        <v>0.04888271385466341</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03059635942465575</v>
+        <v>0.0340374349111361</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02875624213700561</v>
+        <v>0.02706754057755873</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.00750970836967915</v>
+        <v>-0.00489505655924084</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.06924926452539573</v>
+        <v>-0.0566754010805395</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02345957269629694</v>
+        <v>0.02521145384583363</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07224784799443305</v>
+        <v>0.07204813760184801</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01238634158132593</v>
+        <v>-0.01053330809819069</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.04310797426901932</v>
+        <v>-0.03717929177905889</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.07792358103408359</v>
+        <v>-0.06726217513996582</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06855969555104821</v>
+        <v>0.07011527702599592</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07025365153918653</v>
+        <v>0.07193827447259506</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05577475264131273</v>
+        <v>0.05319354982092881</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07658135466897838</v>
+        <v>0.07942533984383919</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05905847351633357</v>
+        <v>0.06144788407830552</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1043208762095007</v>
+        <v>0.07585266957814304</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.03179857992531292</v>
+        <v>-0.02881339884571745</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01667722506556422</v>
+        <v>0.01683851702568571</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.004526045388279737</v>
+        <v>-0.005728774927578519</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01648338108291184</v>
+        <v>0.01610226427459555</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02995211489365769</v>
+        <v>0.02294572417536276</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.02648109598566048</v>
+        <v>-0.0221683169301962</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.06352909070948802</v>
+        <v>-0.06879336570587058</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02601388668070084</v>
+        <v>0.01882577654341023</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001073226763926525</v>
+        <v>-0.007945162934431186</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.02099825952236134</v>
+        <v>-0.02711440004087012</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.04727260101113926</v>
+        <v>-0.05641117945311341</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.08139807031418138</v>
+        <v>-0.0733885287754093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.103003084696228</v>
+        <v>-0.1041093942764987</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.08332380897952964</v>
+        <v>0.08131643239271596</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03610061686049243</v>
+        <v>0.04157546475720989</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.04547968881871365</v>
+        <v>-0.02630918784592106</v>
       </c>
     </row>
     <row r="6">
@@ -1111,118 +1111,118 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.09471263459993598</v>
+        <v>-0.08393553397886809</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.01895352322346457</v>
+        <v>-0.01173118333885382</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04915779677378923</v>
+        <v>0.04085650046777985</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06912092985689866</v>
+        <v>-0.07424450085306426</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05758783770356833</v>
+        <v>0.05196809586958871</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0719621823878321</v>
+        <v>-0.07033239849880712</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08880099474243784</v>
+        <v>-0.09453929690764627</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.01256841003039777</v>
+        <v>-0.009347088792624492</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.03660401013857464</v>
+        <v>-0.0649883253811966</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0737868608839939</v>
+        <v>-0.06959229698893619</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03014227038748109</v>
+        <v>0.02334261858630251</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06263954295873884</v>
+        <v>0.06248730417561048</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.05897596752624527</v>
+        <v>-0.05091874323864833</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04844395589695266</v>
+        <v>0.04481940286482272</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09088138806438163</v>
+        <v>0.08414735376130525</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.06695577066054076</v>
+        <v>-0.0712437479305154</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0741313952174764</v>
+        <v>-0.07949703261161864</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0836052796918374</v>
+        <v>-0.08699189914159085</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09542417418395215</v>
+        <v>-0.09606298406842213</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0679081996556114</v>
+        <v>-0.06821328171500732</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3080274014433118</v>
+        <v>-0.2256414070648119</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.09324137532760718</v>
+        <v>-0.102254639188736</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.09393218105426299</v>
+        <v>-0.09846783867459925</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.02358307435123869</v>
+        <v>-0.01444029485835702</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0985089003724129</v>
+        <v>-0.08256892662023653</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.08199200616907877</v>
+        <v>-0.09338577070188743</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1568634455164448</v>
+        <v>-0.1422556631117435</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.05740204730585814</v>
+        <v>0.03869640244971694</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.06922664571048009</v>
+        <v>-0.0595489065725719</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07182468346390714</v>
+        <v>0.06051838688585841</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1246760319422253</v>
+        <v>0.1111759214855886</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.06402858015334047</v>
+        <v>-0.02846033197263121</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0661143761866599</v>
+        <v>0.02784505313925478</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.1251391444767959</v>
+        <v>-0.1147404779317038</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1633225378394353</v>
+        <v>0.1374010737681006</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.001336323813537968</v>
+        <v>-0.02787001231212922</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.05636340380248044</v>
+        <v>-0.04658099815293717</v>
       </c>
     </row>
     <row r="7">
@@ -1232,118 +1232,118 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01094279151377623</v>
+        <v>0.01470941782638088</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07056816740915545</v>
+        <v>0.07730443382765217</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002903920487998338</v>
+        <v>0.005514093251299968</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01478174307360012</v>
+        <v>0.006023523174550668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05758783770356833</v>
+        <v>0.05196809586958871</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006621804644217221</v>
+        <v>-0.001497065974583933</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01766410160685192</v>
+        <v>0.01028999097148224</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.01349433631720457</v>
+        <v>-0.0219743915091775</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08272956198372718</v>
+        <v>0.06660276390295404</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04260829481786334</v>
+        <v>-0.03930335984850136</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02825873574446769</v>
+        <v>-0.03010437258245686</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05808031547934698</v>
+        <v>-0.06128978434405703</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01294111337831266</v>
+        <v>0.02449095816739147</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.00921726136899719</v>
+        <v>-0.01543738939654837</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.13985292221482</v>
+        <v>0.08721438650986772</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.07679923549225538</v>
+        <v>-0.07330875766291713</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07709631920584849</v>
+        <v>-0.07274635950360019</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.08448475105759734</v>
+        <v>-0.07760486908117939</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09923791531797901</v>
+        <v>-0.09531441563300798</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.08643468856102668</v>
+        <v>-0.07778784043314969</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01409723478656842</v>
+        <v>0.01269487255548205</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0476319274852907</v>
+        <v>0.04017693136809264</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.09826086365034556</v>
+        <v>-0.09467360305488408</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.03719030810335459</v>
+        <v>-0.03482708249705305</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.08545045103224452</v>
+        <v>-0.07387512990463718</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0332007717694827</v>
+        <v>0.02489625873248458</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.1672950624436932</v>
+        <v>-0.1218607487113919</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0422735433401069</v>
+        <v>0.03333834090829432</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.03935582184129265</v>
+        <v>0.02665649647527528</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05765369378247829</v>
+        <v>0.04997298960377877</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.05856342167310739</v>
+        <v>0.05343478797322928</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01490465596927739</v>
+        <v>0.01355434473537971</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.03260566627404664</v>
+        <v>-0.03302448878774304</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.07859417340390126</v>
+        <v>-0.07216711590527908</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.03393762895137785</v>
+        <v>0.03792875946020183</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.005753641990902556</v>
+        <v>0.008140878375632267</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.02507077126245716</v>
+        <v>-0.03227057279931734</v>
       </c>
     </row>
     <row r="8">
@@ -1359,16 +1359,16 @@
         <v>-0.05910584493566232</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07829120642947386</v>
+        <v>0.07795758701857826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04849656045851726</v>
+        <v>0.04888271385466341</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0719621823878321</v>
+        <v>-0.07033239849880712</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006621804644217221</v>
+        <v>-0.001497065974583933</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1380,10 +1380,10 @@
         <v>-0.1113334621458544</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1296237759035007</v>
+        <v>0.1293671975807223</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2035128107873063</v>
+        <v>0.2132836111565168</v>
       </c>
       <c r="M8" t="n">
         <v>-0.1695199125415192</v>
@@ -1392,13 +1392,13 @@
         <v>-0.08561405610898885</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2210889381621089</v>
+        <v>-0.2339945454254462</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.105650683998234</v>
+        <v>-0.1039954889407942</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6009898622880098</v>
+        <v>-0.6330307771638137</v>
       </c>
       <c r="R8" t="n">
         <v>0.6495093731720535</v>
@@ -1416,7 +1416,7 @@
         <v>0.5892857337991374</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01980562760810591</v>
+        <v>-0.04430764159859078</v>
       </c>
       <c r="X8" t="n">
         <v>0.09635670896483021</v>
@@ -1434,7 +1434,7 @@
         <v>0.1942392998942037</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2252833087067666</v>
+        <v>0.2014552355992557</v>
       </c>
       <c r="AD8" t="n">
         <v>0.2024936626155379</v>
@@ -1452,19 +1452,19 @@
         <v>-0.2116886054896172</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.1752383963733126</v>
+        <v>-0.1702429951088437</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1251919142871922</v>
+        <v>0.1202867638719387</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.06603468240498915</v>
+        <v>0.06555470531243922</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.005225255157525568</v>
+        <v>-0.006889216304495412</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.1074469823751557</v>
+        <v>-0.06430633081024528</v>
       </c>
     </row>
     <row r="9">
@@ -1480,16 +1480,16 @@
         <v>0.03930570419804762</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.01986544037384717</v>
+        <v>-0.01487887442821797</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03059635942465575</v>
+        <v>0.0340374349111361</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08880099474243784</v>
+        <v>-0.09453929690764627</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01766410160685192</v>
+        <v>0.01028999097148224</v>
       </c>
       <c r="H9" t="n">
         <v>0.1440991203929681</v>
@@ -1501,10 +1501,10 @@
         <v>-0.07207758533752003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1975197969144622</v>
+        <v>0.1962071362337778</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3918042810480203</v>
+        <v>0.3896661866866414</v>
       </c>
       <c r="M9" t="n">
         <v>-0.04787377945492798</v>
@@ -1513,13 +1513,13 @@
         <v>-0.06625035666044633</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2084839120671803</v>
+        <v>-0.1888705581872125</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.08040146594205887</v>
+        <v>-0.0641463689468451</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1857691820083897</v>
+        <v>-0.1725348574171338</v>
       </c>
       <c r="R9" t="n">
         <v>0.2038607729265072</v>
@@ -1537,7 +1537,7 @@
         <v>0.09437054607279161</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1439168900356151</v>
+        <v>0.1439864512824331</v>
       </c>
       <c r="X9" t="n">
         <v>0.2098566399435249</v>
@@ -1555,7 +1555,7 @@
         <v>0.1927643030952766</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1558613091720537</v>
+        <v>0.1430958204714739</v>
       </c>
       <c r="AD9" t="n">
         <v>0.09097128991165858</v>
@@ -1573,19 +1573,19 @@
         <v>-0.07924387637618892</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.09698478758265774</v>
+        <v>-0.09216256428026545</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.156123524679657</v>
+        <v>0.1465792869191176</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.03254281852133409</v>
+        <v>-0.0342765238618274</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0160119415029926</v>
+        <v>0.01760323797158125</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.03707083945259072</v>
+        <v>-0.03184953565680757</v>
       </c>
     </row>
     <row r="10">
@@ -1601,16 +1601,16 @@
         <v>0.1083157273134549</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03076628385097013</v>
+        <v>0.02961069733445537</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02875624213700561</v>
+        <v>0.02706754057755873</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01256841003039777</v>
+        <v>-0.009347088792624492</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01349433631720457</v>
+        <v>-0.0219743915091775</v>
       </c>
       <c r="H10" t="n">
         <v>-0.1113334621458544</v>
@@ -1622,10 +1622,10 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2406665570196045</v>
+        <v>0.2405545934196641</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1733866681621049</v>
+        <v>-0.1738748056281286</v>
       </c>
       <c r="M10" t="n">
         <v>0.1565696961269441</v>
@@ -1634,13 +1634,13 @@
         <v>0.1091926590536524</v>
       </c>
       <c r="O10" t="n">
-        <v>0.000636998348837337</v>
+        <v>-0.02795332654270893</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03614653203351041</v>
+        <v>0.03248280586311813</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1451425946001771</v>
+        <v>0.1346927411080981</v>
       </c>
       <c r="R10" t="n">
         <v>-0.1241788706453177</v>
@@ -1658,7 +1658,7 @@
         <v>-0.1144068674291582</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03775815458202833</v>
+        <v>-0.007436891321763069</v>
       </c>
       <c r="X10" t="n">
         <v>0.2435931428722011</v>
@@ -1676,7 +1676,7 @@
         <v>-0.01091088926924702</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1293854443690504</v>
+        <v>0.1062440547112405</v>
       </c>
       <c r="AD10" t="n">
         <v>-0.03099990217719134</v>
@@ -1694,19 +1694,19 @@
         <v>0.005251271649771932</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.04040255342109172</v>
+        <v>-0.03858567205224968</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.04129710087961907</v>
+        <v>0.04152788268831505</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.02866247292563552</v>
+        <v>-0.02718709560970321</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.04907419445206011</v>
+        <v>-0.05380690949701126</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3577912521557281</v>
+        <v>0.1634438845988278</v>
       </c>
     </row>
     <row r="11">
@@ -1716,118 +1716,118 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0272098233524093</v>
+        <v>0.02746506530380317</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.06172449749494453</v>
+        <v>-0.06201832835607052</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03524486871065791</v>
+        <v>0.03740833441756483</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.00750970836967915</v>
+        <v>-0.00489505655924084</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.03660401013857464</v>
+        <v>-0.0649883253811966</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08272956198372718</v>
+        <v>0.06660276390295404</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1296237759035007</v>
+        <v>0.1293671975807223</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1975197969144622</v>
+        <v>0.1962071362337778</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2406665570196045</v>
+        <v>0.2405545934196641</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.223628622586687</v>
+        <v>0.2070915009116709</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01837157768120101</v>
+        <v>-0.01808099573075932</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0334901062768518</v>
+        <v>-0.03334532824267672</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3100266850658022</v>
+        <v>-0.2547483606390379</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1234632364597218</v>
+        <v>-0.09954985678944919</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2767500070924492</v>
+        <v>-0.1979435442490809</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1892427999242341</v>
+        <v>0.1881442814276418</v>
       </c>
       <c r="S11" t="n">
-        <v>0.194637676464913</v>
+        <v>0.1932915478080863</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1720042651723676</v>
+        <v>0.1708978169147425</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2055244060984702</v>
+        <v>0.2044856040375728</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1841004317784382</v>
+        <v>0.1830665931287828</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.07628283409426095</v>
+        <v>-0.0226524988874838</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8508750654999802</v>
+        <v>0.8427227209391467</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1723029501531297</v>
+        <v>0.1720154310958033</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.08556107913042546</v>
+        <v>0.08543742458137556</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2197894965876363</v>
+        <v>0.2173170408073755</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3564100840209308</v>
+        <v>0.3559786206534365</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.209527441834656</v>
+        <v>0.1627752656259844</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.221061671872768</v>
+        <v>0.2204910489099894</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.2254565976244682</v>
+        <v>0.2244245402251309</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2177088933345541</v>
+        <v>0.2167512360872801</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.21983081610202</v>
+        <v>0.2189806334906803</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.009860795915760247</v>
+        <v>0.01061327966460778</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.03813344553728248</v>
+        <v>-0.03895475414331239</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.03647408130117411</v>
+        <v>0.03067869317447792</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.05985992870003543</v>
+        <v>0.05637662508521338</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.01154456506168584</v>
+        <v>-0.008939013383730335</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.1164253945870401</v>
+        <v>0.09282759802525414</v>
       </c>
     </row>
     <row r="12">
@@ -1837,118 +1837,118 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04824905490442002</v>
+        <v>0.04879151513855512</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.03119773000218447</v>
+        <v>-0.01660318925918855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03833246208139141</v>
+        <v>0.03498738793209868</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06924926452539573</v>
+        <v>-0.0566754010805395</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0737868608839939</v>
+        <v>-0.06959229698893619</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.04260829481786334</v>
+        <v>-0.03930335984850136</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2035128107873063</v>
+        <v>0.2132836111565168</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3918042810480203</v>
+        <v>0.3896661866866414</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1733866681621049</v>
+        <v>-0.1738748056281286</v>
       </c>
       <c r="K12" t="n">
-        <v>0.223628622586687</v>
+        <v>0.2070915009116709</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09052165181234689</v>
+        <v>-0.08678905028176048</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1325478792278374</v>
+        <v>-0.1200105344451503</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3445017055776788</v>
+        <v>-0.2619005168806267</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2072395357155103</v>
+        <v>-0.1720264482274338</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.3846743288924173</v>
+        <v>-0.3271382312373787</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3041003486640713</v>
+        <v>0.3070291067404715</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3051373646832291</v>
+        <v>0.3087614499526651</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2909437367477026</v>
+        <v>0.2925048235465266</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2715362449326886</v>
+        <v>0.2841760453546149</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2231057361652948</v>
+        <v>0.2359853270481234</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1065773874425495</v>
+        <v>0.1215164888701513</v>
       </c>
       <c r="X12" t="n">
-        <v>0.264887683480386</v>
+        <v>0.2457923779705562</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2174785641642931</v>
+        <v>0.1974713399048637</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.03396685823247717</v>
+        <v>0.0265370060296301</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1474878257325595</v>
+        <v>0.1475975061688915</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2716088677710085</v>
+        <v>0.2557033660047048</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.08050134038835562</v>
+        <v>0.06642931172997589</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1938951997718622</v>
+        <v>0.1927250506512222</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2086297293331689</v>
+        <v>0.2044999761707263</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2255341812426294</v>
+        <v>0.2266983494827063</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2161275567975152</v>
+        <v>0.2235550565729793</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.01587399693792929</v>
+        <v>-0.009870238675361374</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.0212890779159672</v>
+        <v>-0.03356186871102722</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1178945907209771</v>
+        <v>0.1063998781326855</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.03026562606806254</v>
+        <v>-0.02167657846621577</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.03846968406239749</v>
+        <v>-0.03099691021701918</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.1285314205501864</v>
+        <v>-0.08966085872312413</v>
       </c>
     </row>
     <row r="13">
@@ -1964,16 +1964,16 @@
         <v>-0.0823706935463982</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.05048280087593122</v>
+        <v>-0.04876633219291477</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02345957269629694</v>
+        <v>0.02521145384583363</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03014227038748109</v>
+        <v>0.02334261858630251</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.02825873574446769</v>
+        <v>-0.03010437258245686</v>
       </c>
       <c r="H13" t="n">
         <v>-0.1695199125415192</v>
@@ -1985,10 +1985,10 @@
         <v>0.1565696961269441</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.01837157768120101</v>
+        <v>-0.01808099573075932</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.09052165181234689</v>
+        <v>-0.08678905028176048</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1997,13 +1997,13 @@
         <v>0.7731324161460255</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1799232813646809</v>
+        <v>0.1817241381438567</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.07234738549522382</v>
+        <v>-0.06236313286645685</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.211643589434248</v>
+        <v>0.1859401557196712</v>
       </c>
       <c r="R13" t="n">
         <v>-0.210149125915215</v>
@@ -2021,7 +2021,7 @@
         <v>-0.1820533318924092</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1421590866299141</v>
+        <v>0.1689604406149494</v>
       </c>
       <c r="X13" t="n">
         <v>0.05912454148186107</v>
@@ -2039,7 +2039,7 @@
         <v>-0.1562278907988984</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1640729781233963</v>
+        <v>-0.1413878619659363</v>
       </c>
       <c r="AD13" t="n">
         <v>-0.1429864077391405</v>
@@ -2057,19 +2057,19 @@
         <v>0.0510286854117552</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01147320186348751</v>
+        <v>0.01094180656881368</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0106415171849012</v>
+        <v>0.009288825802711474</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.02503388743247075</v>
+        <v>-0.02610901532063269</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.07497304633080538</v>
+        <v>0.08300859760573071</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.05248787567619771</v>
+        <v>0.02348216410198609</v>
       </c>
     </row>
     <row r="14">
@@ -2085,16 +2085,16 @@
         <v>-0.1487514601245411</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.02447886084986306</v>
+        <v>-0.02416072415611886</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07224784799443305</v>
+        <v>0.07204813760184801</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06263954295873884</v>
+        <v>0.06248730417561048</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.05808031547934698</v>
+        <v>-0.06128978434405703</v>
       </c>
       <c r="H14" t="n">
         <v>-0.08561405610898885</v>
@@ -2106,10 +2106,10 @@
         <v>0.1091926590536524</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0334901062768518</v>
+        <v>-0.03334532824267672</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1325478792278374</v>
+        <v>-0.1200105344451503</v>
       </c>
       <c r="M14" t="n">
         <v>0.7731324161460255</v>
@@ -2118,13 +2118,13 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1228414204321888</v>
+        <v>0.1239271635034259</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.04230099374698858</v>
+        <v>-0.03605743299504476</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.143660065510681</v>
+        <v>0.1115860517435321</v>
       </c>
       <c r="R14" t="n">
         <v>-0.1144213681091044</v>
@@ -2142,7 +2142,7 @@
         <v>-0.1338169710530315</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03725383156322876</v>
+        <v>0.05728140413728756</v>
       </c>
       <c r="X14" t="n">
         <v>0.01660508474728901</v>
@@ -2160,7 +2160,7 @@
         <v>-0.127314590874058</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.1923933713318311</v>
+        <v>-0.17163041981066</v>
       </c>
       <c r="AD14" t="n">
         <v>-0.1164812353945424</v>
@@ -2178,19 +2178,19 @@
         <v>0.003486093111072676</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.0327574618089554</v>
+        <v>-0.03146695457714797</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.008376228111177872</v>
+        <v>0.007907600891729346</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.02519420189809373</v>
+        <v>-0.02502656063954326</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.04450979796228239</v>
+        <v>0.04814317277006933</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.05022381199695129</v>
+        <v>0.02892413519219711</v>
       </c>
     </row>
     <row r="15">
@@ -2200,118 +2200,118 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1337581119984088</v>
+        <v>-0.1468008025855293</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03503520605230256</v>
+        <v>0.008059420081243192</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03444272703738956</v>
+        <v>-0.02014874515684935</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01238634158132593</v>
+        <v>-0.01053330809819069</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05897596752624527</v>
+        <v>-0.05091874323864833</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01294111337831266</v>
+        <v>0.02449095816739147</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2210889381621089</v>
+        <v>-0.2339945454254462</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2084839120671803</v>
+        <v>-0.1888705581872125</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000636998348837337</v>
+        <v>-0.02795332654270893</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3100266850658022</v>
+        <v>-0.2547483606390379</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3445017055776788</v>
+        <v>-0.2619005168806267</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1799232813646809</v>
+        <v>0.1817241381438567</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1228414204321888</v>
+        <v>0.1239271635034259</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2242992653305121</v>
+        <v>0.2112794945303412</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3734550718655288</v>
+        <v>0.3157528252737426</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.3342778260406369</v>
+        <v>-0.3269961014168094</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3465324058445168</v>
+        <v>-0.3371566754556039</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3342594641360981</v>
+        <v>-0.3193913177601773</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3214660269486925</v>
+        <v>-0.3362613153245388</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.265200393573824</v>
+        <v>-0.2928558659360858</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.05147612245713113</v>
+        <v>-0.04960004206214112</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2663211255313009</v>
+        <v>-0.2122752304793286</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.2053883765242343</v>
+        <v>-0.1028196553438033</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.1660547610768363</v>
+        <v>-0.1626606320334593</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.2309820319890769</v>
+        <v>-0.2082311121749761</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2877419573418973</v>
+        <v>-0.2287004548617354</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.06248863027160362</v>
+        <v>-0.0570327130047179</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2120220076132207</v>
+        <v>-0.1900261927608814</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.2774902585207192</v>
+        <v>-0.2468981265914317</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2245796735081942</v>
+        <v>-0.2052821062617807</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.1899924043024699</v>
+        <v>-0.1829445672900349</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.1703347643669292</v>
+        <v>0.2290894978090072</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.05278542291747129</v>
+        <v>0.08400077205681279</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.09393211872795122</v>
+        <v>-0.07492660510083043</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.03196941172687597</v>
+        <v>-0.01257276528809492</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.08802182794324812</v>
+        <v>0.1206405395773167</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.01489742231702872</v>
+        <v>-0.05536307153215934</v>
       </c>
     </row>
     <row r="16">
@@ -2321,118 +2321,118 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.05841151381732715</v>
+        <v>-0.05540373604059472</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1550102215298965</v>
+        <v>-0.1415285512189099</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.01456019065820884</v>
+        <v>-0.01549428869572865</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04310797426901932</v>
+        <v>-0.03717929177905889</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04844395589695266</v>
+        <v>0.04481940286482272</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.00921726136899719</v>
+        <v>-0.01543738939654837</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.105650683998234</v>
+        <v>-0.1039954889407942</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08040146594205887</v>
+        <v>-0.0641463689468451</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03614653203351041</v>
+        <v>0.03248280586311813</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1234632364597218</v>
+        <v>-0.09954985678944919</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2072395357155103</v>
+        <v>-0.1720264482274338</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07234738549522382</v>
+        <v>-0.06236313286645685</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04230099374698858</v>
+        <v>-0.03605743299504476</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2242992653305121</v>
+        <v>0.2112794945303412</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.103662681309758</v>
+        <v>0.1072409261771442</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.06267095724036401</v>
+        <v>-0.0610826436895231</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0777489423387635</v>
+        <v>-0.07459281209094817</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08864524951902987</v>
+        <v>-0.08003682279170246</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1113262439340893</v>
+        <v>-0.1074178905435457</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.07955821546061828</v>
+        <v>-0.08195301164959726</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03264358965751916</v>
+        <v>0.003632044995344824</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.09363831581240013</v>
+        <v>-0.0677445533828573</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.01341809137408593</v>
+        <v>0.01403466150327604</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.02827070456449379</v>
+        <v>0.02424455170179688</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.159064556454874</v>
+        <v>-0.1348336042874315</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.08713835783081056</v>
+        <v>-0.07037337570466971</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.03529090526831108</v>
+        <v>-0.03207971387869528</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0006264195229262234</v>
+        <v>-0.0008729402421238404</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.05841562979474375</v>
+        <v>-0.05211464091694891</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.09697566414782452</v>
+        <v>-0.08883271402400218</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.06010359439647176</v>
+        <v>-0.06054585705728616</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.06052424569760188</v>
+        <v>0.07621490561587219</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.1119950397335723</v>
+        <v>0.1099839020297817</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01504530731516486</v>
+        <v>0.0178665587082704</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.05402500862980715</v>
+        <v>-0.04497744753174134</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02290391387001612</v>
+        <v>0.02757258923106162</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.02475817364149503</v>
+        <v>0.005260498615053966</v>
       </c>
     </row>
     <row r="17">
@@ -2442,118 +2442,118 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1784129385270832</v>
+        <v>-0.19223126410265</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1898946962036527</v>
+        <v>0.1384407829480833</v>
       </c>
       <c r="D17" t="n">
-        <v>0.007387010307146017</v>
+        <v>0.0280904804947647</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07792358103408359</v>
+        <v>-0.06726217513996582</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09088138806438163</v>
+        <v>0.08414735376130525</v>
       </c>
       <c r="G17" t="n">
-        <v>0.13985292221482</v>
+        <v>0.08721438650986772</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6009898622880098</v>
+        <v>-0.6330307771638137</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1857691820083897</v>
+        <v>-0.1725348574171338</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1451425946001771</v>
+        <v>0.1346927411080981</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2767500070924492</v>
+        <v>-0.1979435442490809</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3846743288924173</v>
+        <v>-0.3271382312373787</v>
       </c>
       <c r="M17" t="n">
-        <v>0.211643589434248</v>
+        <v>0.1859401557196712</v>
       </c>
       <c r="N17" t="n">
-        <v>0.143660065510681</v>
+        <v>0.1115860517435321</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3734550718655288</v>
+        <v>0.3157528252737426</v>
       </c>
       <c r="P17" t="n">
-        <v>0.103662681309758</v>
+        <v>0.1072409261771442</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.9346653604095465</v>
+        <v>-0.9558338578544336</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9352698645726282</v>
+        <v>-0.9561464930821471</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9150391421402607</v>
+        <v>-0.9372906401552763</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9148629921628357</v>
+        <v>-0.9371990357988067</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8688889092975121</v>
+        <v>-0.8878974017096656</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0007305852895109026</v>
+        <v>0.004788681520092323</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2457413415057402</v>
+        <v>-0.1836833925538437</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.8689932202883281</v>
+        <v>-0.2623839058356249</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.02717883467076136</v>
+        <v>-0.05076763282592284</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.2151276336243488</v>
+        <v>-0.2202111879270066</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.349984178540005</v>
+        <v>-0.2591586431542123</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.2754444639041589</v>
+        <v>-0.2361604892088111</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.2784924089310495</v>
+        <v>-0.2377902305454056</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.3008265065722057</v>
+        <v>-0.264167173744809</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.3014803137141585</v>
+        <v>-0.2573460553043674</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.2436411680752137</v>
+        <v>-0.2127048209960673</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.09239450980788627</v>
+        <v>0.1437570260888105</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.1365750767395381</v>
+        <v>0.1504799996820795</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.1999930150571219</v>
+        <v>-0.1938288890453189</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.1118327614878394</v>
+        <v>-0.07132893122846569</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.06095421984208246</v>
+        <v>0.04081703778331965</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.2164468210718996</v>
+        <v>0.1337823610655039</v>
       </c>
     </row>
     <row r="18">
@@ -2569,16 +2569,16 @@
         <v>-0.1274492471065007</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02290608424599904</v>
+        <v>0.02444212152457531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06855969555104821</v>
+        <v>0.07011527702599592</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06695577066054076</v>
+        <v>-0.0712437479305154</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07679923549225538</v>
+        <v>-0.07330875766291713</v>
       </c>
       <c r="H18" t="n">
         <v>0.6495093731720535</v>
@@ -2590,10 +2590,10 @@
         <v>-0.1241788706453177</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1892427999242341</v>
+        <v>0.1881442814276418</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3041003486640713</v>
+        <v>0.3070291067404715</v>
       </c>
       <c r="M18" t="n">
         <v>-0.210149125915215</v>
@@ -2602,13 +2602,13 @@
         <v>-0.1144213681091044</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3342778260406369</v>
+        <v>-0.3269961014168094</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.06267095724036401</v>
+        <v>-0.0610826436895231</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9346653604095465</v>
+        <v>-0.9558338578544336</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2626,7 +2626,7 @@
         <v>0.8568929812324875</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.02156148662389396</v>
+        <v>-0.02132225316385617</v>
       </c>
       <c r="X18" t="n">
         <v>0.1746906921759226</v>
@@ -2644,7 +2644,7 @@
         <v>0.2658354317004078</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2813156212314002</v>
+        <v>0.2533177657518206</v>
       </c>
       <c r="AD18" t="n">
         <v>0.2437646087875831</v>
@@ -2662,19 +2662,19 @@
         <v>-0.1675310295187097</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.1911945001313806</v>
+        <v>-0.1855669612761618</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2220714710028329</v>
+        <v>0.2131851614955034</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.09376647633867986</v>
+        <v>0.09114767049489604</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.0529204742474713</v>
+        <v>-0.04926556303736935</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.1873846917596958</v>
+        <v>-0.1369379216734689</v>
       </c>
     </row>
     <row r="19">
@@ -2690,16 +2690,16 @@
         <v>-0.1417484735386519</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02492493770271854</v>
+        <v>0.02662024472783422</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07025365153918653</v>
+        <v>0.07193827447259506</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0741313952174764</v>
+        <v>-0.07949703261161864</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07709631920584849</v>
+        <v>-0.07274635950360019</v>
       </c>
       <c r="H19" t="n">
         <v>0.6495739413407626</v>
@@ -2711,10 +2711,10 @@
         <v>-0.1226661627845969</v>
       </c>
       <c r="K19" t="n">
-        <v>0.194637676464913</v>
+        <v>0.1932915478080863</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3051373646832291</v>
+        <v>0.3087614499526651</v>
       </c>
       <c r="M19" t="n">
         <v>-0.2033685715181316</v>
@@ -2723,13 +2723,13 @@
         <v>-0.1106198952002733</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3465324058445168</v>
+        <v>-0.3371566754556039</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0777489423387635</v>
+        <v>-0.07459281209094817</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9352698645726282</v>
+        <v>-0.9561464930821471</v>
       </c>
       <c r="R19" t="n">
         <v>0.9928665174899211</v>
@@ -2747,7 +2747,7 @@
         <v>0.8558250570831188</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.01075940996089148</v>
+        <v>-0.01239057325266972</v>
       </c>
       <c r="X19" t="n">
         <v>0.1770415325023544</v>
@@ -2765,7 +2765,7 @@
         <v>0.2674637253391703</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.290687768225443</v>
+        <v>0.2606496453556167</v>
       </c>
       <c r="AD19" t="n">
         <v>0.2421655093927834</v>
@@ -2783,19 +2783,19 @@
         <v>-0.1669820577555144</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.1905374695487829</v>
+        <v>-0.1858861743209482</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2310744579748674</v>
+        <v>0.2218990933016167</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.1020855286408996</v>
+        <v>0.09925432707567487</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.05011621984621317</v>
+        <v>-0.04620970029816943</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.1964282141661401</v>
+        <v>-0.1442687416081952</v>
       </c>
     </row>
     <row r="20">
@@ -2811,16 +2811,16 @@
         <v>-0.1431980869354525</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02584805745305325</v>
+        <v>0.02557863773821953</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05577475264131273</v>
+        <v>0.05319354982092881</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0836052796918374</v>
+        <v>-0.08699189914159085</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.08448475105759734</v>
+        <v>-0.07760486908117939</v>
       </c>
       <c r="H20" t="n">
         <v>0.5919419551484657</v>
@@ -2832,10 +2832,10 @@
         <v>-0.1234690515207713</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1720042651723676</v>
+        <v>0.1708978169147425</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2909437367477026</v>
+        <v>0.2925048235465266</v>
       </c>
       <c r="M20" t="n">
         <v>-0.1795291957737357</v>
@@ -2844,13 +2844,13 @@
         <v>-0.1039635006214333</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3342594641360981</v>
+        <v>-0.3193913177601773</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.08864524951902987</v>
+        <v>-0.08003682279170246</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9150391421402607</v>
+        <v>-0.9372906401552763</v>
       </c>
       <c r="R20" t="n">
         <v>0.9273247064056973</v>
@@ -2868,7 +2868,7 @@
         <v>0.8295880502763374</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.004797274068916854</v>
+        <v>-0.01912581213836161</v>
       </c>
       <c r="X20" t="n">
         <v>0.1566190998894406</v>
@@ -2886,7 +2886,7 @@
         <v>0.269395779802085</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2539869462266738</v>
+        <v>0.2310365800694171</v>
       </c>
       <c r="AD20" t="n">
         <v>0.2559131004127476</v>
@@ -2904,19 +2904,19 @@
         <v>-0.1090954234540549</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.1295209675592268</v>
+        <v>-0.1264554653918906</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.206549783567091</v>
+        <v>0.2003850177112176</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.07912028713796745</v>
+        <v>0.08228642455195354</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.05520368317252184</v>
+        <v>-0.06209343820765205</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.1806767078732945</v>
+        <v>-0.1324375143282568</v>
       </c>
     </row>
     <row r="21">
@@ -2932,16 +2932,16 @@
         <v>-0.09720830208630422</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.02546250330274214</v>
+        <v>-0.02192240387799482</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07658135466897838</v>
+        <v>0.07942533984383919</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09542417418395215</v>
+        <v>-0.09606298406842213</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09923791531797901</v>
+        <v>-0.09531441563300798</v>
       </c>
       <c r="H21" t="n">
         <v>0.6468188946021095</v>
@@ -2953,10 +2953,10 @@
         <v>-0.1176796541084856</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2055244060984702</v>
+        <v>0.2044856040375728</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2715362449326886</v>
+        <v>0.2841760453546149</v>
       </c>
       <c r="M21" t="n">
         <v>-0.2342702161584364</v>
@@ -2965,13 +2965,13 @@
         <v>-0.1498117854508859</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3214660269486925</v>
+        <v>-0.3362613153245388</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1113262439340893</v>
+        <v>-0.1074178905435457</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9148629921628357</v>
+        <v>-0.9371990357988067</v>
       </c>
       <c r="R21" t="n">
         <v>0.9399723121033041</v>
@@ -2989,7 +2989,7 @@
         <v>0.898281431259045</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01469337385491111</v>
+        <v>-0.0009543618344151881</v>
       </c>
       <c r="X21" t="n">
         <v>0.174385109121811</v>
@@ -3007,7 +3007,7 @@
         <v>0.251094614413955</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.3037450588124693</v>
+        <v>0.2707043732912264</v>
       </c>
       <c r="AD21" t="n">
         <v>0.238082911098724</v>
@@ -3025,19 +3025,19 @@
         <v>-0.1811976023117671</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.2002201447242642</v>
+        <v>-0.1948842633346706</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.2006215124812954</v>
+        <v>0.1891440174168869</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.1207274448860888</v>
+        <v>0.1165985744146733</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.0718097083205487</v>
+        <v>-0.06785579478718096</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.1935109417640029</v>
+        <v>-0.1393279899529387</v>
       </c>
     </row>
     <row r="22">
@@ -3053,16 +3053,16 @@
         <v>-0.122279895129924</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.049731060955252</v>
+        <v>-0.04619623319854044</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05905847351633357</v>
+        <v>0.06144788407830552</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0679081996556114</v>
+        <v>-0.06821328171500732</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08643468856102668</v>
+        <v>-0.07778784043314969</v>
       </c>
       <c r="H22" t="n">
         <v>0.5892857337991374</v>
@@ -3074,10 +3074,10 @@
         <v>-0.1144068674291582</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1841004317784382</v>
+        <v>0.1830665931287828</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2231057361652948</v>
+        <v>0.2359853270481234</v>
       </c>
       <c r="M22" t="n">
         <v>-0.1820533318924092</v>
@@ -3086,13 +3086,13 @@
         <v>-0.1338169710530315</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.265200393573824</v>
+        <v>-0.2928558659360858</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.07955821546061828</v>
+        <v>-0.08195301164959726</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.8688889092975121</v>
+        <v>-0.8878974017096656</v>
       </c>
       <c r="R22" t="n">
         <v>0.8568929812324875</v>
@@ -3110,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.001160803226066221</v>
+        <v>-0.01317240814825448</v>
       </c>
       <c r="X22" t="n">
         <v>0.1256662168942605</v>
@@ -3128,7 +3128,7 @@
         <v>0.2282157341176923</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.1956212603711216</v>
+        <v>0.1817944040904322</v>
       </c>
       <c r="AD22" t="n">
         <v>0.2162923309641856</v>
@@ -3146,19 +3146,19 @@
         <v>-0.1613488778398614</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.1787565341617213</v>
+        <v>-0.170776994770234</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.1477219894042046</v>
+        <v>0.1370548888055075</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.08352702909726634</v>
+        <v>0.07783981400362308</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.06047380963377873</v>
+        <v>-0.05294457798265444</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.1948893492995449</v>
+        <v>-0.1346534173060699</v>
       </c>
     </row>
     <row r="23">
@@ -3168,118 +3168,118 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1345780502869412</v>
+        <v>0.1241478225135855</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.03850370537400002</v>
+        <v>-0.06186766340192854</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04984904678696692</v>
+        <v>-0.03064949227689961</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1043208762095007</v>
+        <v>0.07585266957814304</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3080274014433118</v>
+        <v>-0.2256414070648119</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01409723478656842</v>
+        <v>0.01269487255548205</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.01980562760810591</v>
+        <v>-0.04430764159859078</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1439168900356151</v>
+        <v>0.1439864512824331</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.03775815458202833</v>
+        <v>-0.007436891321763069</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.07628283409426095</v>
+        <v>-0.0226524988874838</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1065773874425495</v>
+        <v>0.1215164888701513</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1421590866299141</v>
+        <v>0.1689604406149494</v>
       </c>
       <c r="N23" t="n">
-        <v>0.03725383156322876</v>
+        <v>0.05728140413728756</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.05147612245713113</v>
+        <v>-0.04960004206214112</v>
       </c>
       <c r="P23" t="n">
-        <v>0.03264358965751916</v>
+        <v>0.003632044995344824</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0007305852895109026</v>
+        <v>0.004788681520092323</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.02156148662389396</v>
+        <v>-0.02132225316385617</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.01075940996089148</v>
+        <v>-0.01239057325266972</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.004797274068916854</v>
+        <v>-0.01912581213836161</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01469337385491111</v>
+        <v>-0.0009543618344151881</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.001160803226066221</v>
+        <v>-0.01317240814825448</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.07367879475652517</v>
+        <v>-0.01153557537283234</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.03812559474925047</v>
+        <v>0.0567668055648027</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1094381860218494</v>
+        <v>0.09445534710787018</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0195879128688369</v>
+        <v>0.02415481994006043</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.006461456031237203</v>
+        <v>0.01503775687714739</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.02417496917203288</v>
+        <v>0.02719695897686685</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.009476920145850651</v>
+        <v>-0.01996585447909614</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.1768893895080537</v>
+        <v>0.1520710186922642</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.006163971522607235</v>
+        <v>-0.01308147950541802</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.04085001499879626</v>
+        <v>-0.06806957715988012</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.04743782672105915</v>
+        <v>-0.02894614355273606</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.07344427226575594</v>
+        <v>-0.04159488933549275</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.1019862331108075</v>
+        <v>0.1161808833535688</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.2360717864576095</v>
+        <v>-0.2122130026936639</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.06570141940374311</v>
+        <v>-0.02544664002816167</v>
       </c>
       <c r="AM23" t="n">
-        <v>-0.01432306653619482</v>
+        <v>-0.0264322039451852</v>
       </c>
     </row>
     <row r="24">
@@ -3295,16 +3295,16 @@
         <v>-0.06837081063659178</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05865768480797615</v>
+        <v>0.05982479211141413</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.03179857992531292</v>
+        <v>-0.02881339884571745</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.09324137532760718</v>
+        <v>-0.102254639188736</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0476319274852907</v>
+        <v>0.04017693136809264</v>
       </c>
       <c r="H24" t="n">
         <v>0.09635670896483021</v>
@@ -3316,10 +3316,10 @@
         <v>0.2435931428722011</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8508750654999802</v>
+        <v>0.8427227209391467</v>
       </c>
       <c r="L24" t="n">
-        <v>0.264887683480386</v>
+        <v>0.2457923779705562</v>
       </c>
       <c r="M24" t="n">
         <v>0.05912454148186107</v>
@@ -3328,13 +3328,13 @@
         <v>0.01660508474728901</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2663211255313009</v>
+        <v>-0.2122752304793286</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.09363831581240013</v>
+        <v>-0.0677445533828573</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2457413415057402</v>
+        <v>-0.1836833925538437</v>
       </c>
       <c r="R24" t="n">
         <v>0.1746906921759226</v>
@@ -3352,7 +3352,7 @@
         <v>0.1256662168942605</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.07367879475652517</v>
+        <v>-0.01153557537283234</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -3370,7 +3370,7 @@
         <v>0.2849194418173898</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2469388157572042</v>
+        <v>0.2101380021943503</v>
       </c>
       <c r="AD24" t="n">
         <v>0.1739611095516026</v>
@@ -3388,19 +3388,19 @@
         <v>0.03247128521635469</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.04961671219776224</v>
+        <v>-0.04611701833105515</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.09804226397202295</v>
+        <v>0.09054420123134811</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.03069142533919158</v>
+        <v>0.02841425414292002</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.0143453522500506</v>
+        <v>-0.0114700008913392</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.07689488514718229</v>
+        <v>0.05998910641119317</v>
       </c>
     </row>
     <row r="25">
@@ -3416,16 +3416,16 @@
         <v>-0.109145531265012</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02857124055848427</v>
+        <v>0.03009571706568123</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01667722506556422</v>
+        <v>0.01683851702568571</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.09393218105426299</v>
+        <v>-0.09846783867459925</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.09826086365034556</v>
+        <v>-0.09467360305488408</v>
       </c>
       <c r="H25" t="n">
         <v>0.1014682095805326</v>
@@ -3437,10 +3437,10 @@
         <v>-0.03166627809695737</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1723029501531297</v>
+        <v>0.1720154310958033</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2174785641642931</v>
+        <v>0.1974713399048637</v>
       </c>
       <c r="M25" t="n">
         <v>-0.08314724579797761</v>
@@ -3449,13 +3449,13 @@
         <v>-0.07009250648773183</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2053883765242343</v>
+        <v>-0.1028196553438033</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01341809137408593</v>
+        <v>0.01403466150327604</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.8689932202883281</v>
+        <v>-0.2623839058356249</v>
       </c>
       <c r="R25" t="n">
         <v>0.2686610979169281</v>
@@ -3473,7 +3473,7 @@
         <v>0.2353661888650143</v>
       </c>
       <c r="W25" t="n">
-        <v>0.03812559474925047</v>
+        <v>0.0567668055648027</v>
       </c>
       <c r="X25" t="n">
         <v>0.1682807635694371</v>
@@ -3491,7 +3491,7 @@
         <v>0.2838088642620377</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.04946701456896676</v>
+        <v>0.05121977197188637</v>
       </c>
       <c r="AD25" t="n">
         <v>0.1475542527561344</v>
@@ -3509,19 +3509,19 @@
         <v>0.1141055122825928</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.01142005906571321</v>
+        <v>0.01397366050773529</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.01597939341233144</v>
+        <v>0.01459935048643615</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.05634425641252028</v>
+        <v>0.05594955270100413</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.02324241148058295</v>
+        <v>-0.01731025347292364</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0.1315621616348011</v>
+        <v>-0.1351918422274742</v>
       </c>
     </row>
     <row r="26">
@@ -3537,16 +3537,16 @@
         <v>0.09450721904717808</v>
       </c>
       <c r="D26" t="n">
-        <v>0.022952246650036</v>
+        <v>0.02210086423804243</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.004526045388279737</v>
+        <v>-0.005728774927578519</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.02358307435123869</v>
+        <v>-0.01444029485835702</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.03719030810335459</v>
+        <v>-0.03482708249705305</v>
       </c>
       <c r="H26" t="n">
         <v>0.04696739214296617</v>
@@ -3558,10 +3558,10 @@
         <v>0.08273763879679547</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08556107913042546</v>
+        <v>0.08543742458137556</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03396685823247717</v>
+        <v>0.0265370060296301</v>
       </c>
       <c r="M26" t="n">
         <v>-0.03751921668040816</v>
@@ -3570,13 +3570,13 @@
         <v>0.01736537720961473</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1660547610768363</v>
+        <v>-0.1626606320334593</v>
       </c>
       <c r="P26" t="n">
-        <v>0.02827070456449379</v>
+        <v>0.02424455170179688</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.02717883467076136</v>
+        <v>-0.05076763282592284</v>
       </c>
       <c r="R26" t="n">
         <v>0.07788673784374597</v>
@@ -3594,7 +3594,7 @@
         <v>0.0620268603724615</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1094381860218494</v>
+        <v>0.09445534710787018</v>
       </c>
       <c r="X26" t="n">
         <v>0.05863226799474909</v>
@@ -3612,7 +3612,7 @@
         <v>0.100379723972125</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.3085601448374495</v>
+        <v>0.2974277295642684</v>
       </c>
       <c r="AD26" t="n">
         <v>0.02116757217355599</v>
@@ -3630,19 +3630,19 @@
         <v>-0.08015080860335548</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.1068816273561675</v>
+        <v>-0.1040131820551513</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.2273766618293648</v>
+        <v>0.2252185624624827</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.004511913593645942</v>
+        <v>0.005564488750545114</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.05416885496615106</v>
+        <v>-0.05722800597492647</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.05555018540259088</v>
+        <v>0.05244120467817286</v>
       </c>
     </row>
     <row r="27">
@@ -3658,16 +3658,16 @@
         <v>0.3931401367310535</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0234822200676378</v>
+        <v>-0.02154627495444019</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01648338108291184</v>
+        <v>0.01610226427459555</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0985089003724129</v>
+        <v>-0.08256892662023653</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.08545045103224452</v>
+        <v>-0.07387512990463718</v>
       </c>
       <c r="H27" t="n">
         <v>0.1398439907324397</v>
@@ -3679,10 +3679,10 @@
         <v>0.08171134295834982</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2197894965876363</v>
+        <v>0.2173170408073755</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1474878257325595</v>
+        <v>0.1475975061688915</v>
       </c>
       <c r="M27" t="n">
         <v>-0.05390648238289666</v>
@@ -3691,13 +3691,13 @@
         <v>-0.002119356070791539</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.2309820319890769</v>
+        <v>-0.2082311121749761</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.159064556454874</v>
+        <v>-0.1348336042874315</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.2151276336243488</v>
+        <v>-0.2202111879270066</v>
       </c>
       <c r="R27" t="n">
         <v>0.2260999680707285</v>
@@ -3715,7 +3715,7 @@
         <v>0.2168238556163936</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0195879128688369</v>
+        <v>0.02415481994006043</v>
       </c>
       <c r="X27" t="n">
         <v>0.2524619655598002</v>
@@ -3733,7 +3733,7 @@
         <v>0.1901202172058218</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.3704284121523467</v>
+        <v>0.3484929361043297</v>
       </c>
       <c r="AD27" t="n">
         <v>0.044737732091778</v>
@@ -3751,19 +3751,19 @@
         <v>-0.1368776841643348</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.1366226559693828</v>
+        <v>-0.1338183402503031</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.1915971443985935</v>
+        <v>0.1789941163618803</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.1003073853843945</v>
+        <v>0.09915067048322244</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.03697518345647147</v>
+        <v>0.03407429456754927</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.0009015844660605205</v>
+        <v>0.01088459472383434</v>
       </c>
     </row>
     <row r="28">
@@ -3779,16 +3779,16 @@
         <v>-0.03729635175521668</v>
       </c>
       <c r="D28" t="n">
-        <v>0.05274772388314103</v>
+        <v>0.04957843309595</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02995211489365769</v>
+        <v>0.02294572417536276</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.08199200616907877</v>
+        <v>-0.09338577070188743</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0332007717694827</v>
+        <v>0.02489625873248458</v>
       </c>
       <c r="H28" t="n">
         <v>0.1942392998942037</v>
@@ -3800,10 +3800,10 @@
         <v>-0.01091088926924702</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3564100840209308</v>
+        <v>0.3559786206534365</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2716088677710085</v>
+        <v>0.2557033660047048</v>
       </c>
       <c r="M28" t="n">
         <v>-0.1562278907988984</v>
@@ -3812,13 +3812,13 @@
         <v>-0.127314590874058</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.2877419573418973</v>
+        <v>-0.2287004548617354</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.08713835783081056</v>
+        <v>-0.07037337570466971</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.349984178540005</v>
+        <v>-0.2591586431542123</v>
       </c>
       <c r="R28" t="n">
         <v>0.2658354317004078</v>
@@ -3836,7 +3836,7 @@
         <v>0.2282157341176923</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.006461456031237203</v>
+        <v>0.01503775687714739</v>
       </c>
       <c r="X28" t="n">
         <v>0.2849194418173898</v>
@@ -3854,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.05428954785187638</v>
+        <v>-0.002826731039281789</v>
       </c>
       <c r="AD28" t="n">
         <v>0.5513046554526563</v>
@@ -3872,19 +3872,19 @@
         <v>0.2976280366672266</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.06983959254208889</v>
+        <v>0.06849065339056694</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.03388433276083041</v>
+        <v>-0.03240622259132252</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.00396103921222094</v>
+        <v>0.00084453577409378</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.01185035880722155</v>
+        <v>-0.01901783765956438</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.0008230545258206735</v>
+        <v>0.01634847735115262</v>
       </c>
     </row>
     <row r="29">
@@ -3894,118 +3894,118 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1438657730990845</v>
+        <v>0.1269846847003911</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1098479626493104</v>
+        <v>0.09346809140231702</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04497097937068635</v>
+        <v>0.03574659532484323</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.02648109598566048</v>
+        <v>-0.0221683169301962</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1568634455164448</v>
+        <v>-0.1422556631117435</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1672950624436932</v>
+        <v>-0.1218607487113919</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2252833087067666</v>
+        <v>0.2014552355992557</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1558613091720537</v>
+        <v>0.1430958204714739</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1293854443690504</v>
+        <v>0.1062440547112405</v>
       </c>
       <c r="K29" t="n">
-        <v>0.209527441834656</v>
+        <v>0.1627752656259844</v>
       </c>
       <c r="L29" t="n">
-        <v>0.08050134038835562</v>
+        <v>0.06642931172997589</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1640729781233963</v>
+        <v>-0.1413878619659363</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.1923933713318311</v>
+        <v>-0.17163041981066</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.06248863027160362</v>
+        <v>-0.0570327130047179</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.03529090526831108</v>
+        <v>-0.03207971387869528</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.2754444639041589</v>
+        <v>-0.2361604892088111</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2813156212314002</v>
+        <v>0.2533177657518206</v>
       </c>
       <c r="S29" t="n">
-        <v>0.290687768225443</v>
+        <v>0.2606496453556167</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2539869462266738</v>
+        <v>0.2310365800694171</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3037450588124693</v>
+        <v>0.2707043732912264</v>
       </c>
       <c r="V29" t="n">
-        <v>0.1956212603711216</v>
+        <v>0.1817944040904322</v>
       </c>
       <c r="W29" t="n">
-        <v>0.02417496917203288</v>
+        <v>0.02719695897686685</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2469388157572042</v>
+        <v>0.2101380021943503</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.04946701456896676</v>
+        <v>0.05121977197188637</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3085601448374495</v>
+        <v>0.2974277295642684</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.3704284121523467</v>
+        <v>0.3484929361043297</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.05428954785187638</v>
+        <v>-0.002826731039281789</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.01602159226565002</v>
+        <v>-0.02476481956181467</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.09831475923365854</v>
+        <v>0.04912212174872113</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.03267384759903268</v>
+        <v>-0.03452605771498241</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.06918710717919123</v>
+        <v>-0.06256241430684921</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.03227396357478368</v>
+        <v>-0.03041741745842462</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.1222341169794451</v>
+        <v>-0.1119919591087561</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.258176204423206</v>
+        <v>0.2271404550801812</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.08790868932269284</v>
+        <v>0.07521081750648492</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.08842910318723335</v>
+        <v>0.07104268120330925</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.02150768262079008</v>
+        <v>-0.01128786384927623</v>
       </c>
     </row>
     <row r="30">
@@ -4021,16 +4021,16 @@
         <v>-0.05659509016403137</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08965074088428525</v>
+        <v>0.08546413368914059</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.06352909070948802</v>
+        <v>-0.06879336570587058</v>
       </c>
       <c r="F30" t="n">
-        <v>0.05740204730585814</v>
+        <v>0.03869640244971694</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0422735433401069</v>
+        <v>0.03333834090829432</v>
       </c>
       <c r="H30" t="n">
         <v>0.2024936626155379</v>
@@ -4042,10 +4042,10 @@
         <v>-0.03099990217719134</v>
       </c>
       <c r="K30" t="n">
-        <v>0.221061671872768</v>
+        <v>0.2204910489099894</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1938951997718622</v>
+        <v>0.1927250506512222</v>
       </c>
       <c r="M30" t="n">
         <v>-0.1429864077391405</v>
@@ -4054,13 +4054,13 @@
         <v>-0.1164812353945424</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.2120220076132207</v>
+        <v>-0.1900261927608814</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0006264195229262234</v>
+        <v>-0.0008729402421238404</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2784924089310495</v>
+        <v>-0.2377902305454056</v>
       </c>
       <c r="R30" t="n">
         <v>0.2437646087875831</v>
@@ -4078,7 +4078,7 @@
         <v>0.2162923309641856</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.009476920145850651</v>
+        <v>-0.01996585447909614</v>
       </c>
       <c r="X30" t="n">
         <v>0.1739611095516026</v>
@@ -4096,7 +4096,7 @@
         <v>0.5513046554526563</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.01602159226565002</v>
+        <v>-0.02476481956181467</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -4114,19 +4114,19 @@
         <v>-0.007425249916527521</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.01409316122927576</v>
+        <v>0.0103967854825519</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.03791500647245184</v>
+        <v>-0.0350886258345296</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.07461267644836189</v>
+        <v>-0.06741420290390326</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.0643148034487168</v>
+        <v>-0.06992193156964867</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.008233524447443708</v>
+        <v>0.04182420721745185</v>
       </c>
     </row>
     <row r="31">
@@ -4142,16 +4142,16 @@
         <v>-0.05159685177048401</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1031362400804397</v>
+        <v>0.09841387610885519</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02601388668070084</v>
+        <v>0.01882577654341023</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06922664571048009</v>
+        <v>-0.0595489065725719</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03935582184129265</v>
+        <v>0.02665649647527528</v>
       </c>
       <c r="H31" t="n">
         <v>0.2555841252688199</v>
@@ -4163,10 +4163,10 @@
         <v>-0.03350400790684007</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2254565976244682</v>
+        <v>0.2244245402251309</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2086297293331689</v>
+        <v>0.2044999761707263</v>
       </c>
       <c r="M31" t="n">
         <v>-0.1437119764356921</v>
@@ -4175,13 +4175,13 @@
         <v>-0.06375382868232632</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.2774902585207192</v>
+        <v>-0.2468981265914317</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.05841562979474375</v>
+        <v>-0.05211464091694891</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.3008265065722057</v>
+        <v>-0.264167173744809</v>
       </c>
       <c r="R31" t="n">
         <v>0.2835532639323152</v>
@@ -4199,7 +4199,7 @@
         <v>0.2556927050597864</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1768893895080537</v>
+        <v>0.1520710186922642</v>
       </c>
       <c r="X31" t="n">
         <v>0.2027415349178901</v>
@@ -4217,7 +4217,7 @@
         <v>0.5383404943484412</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.09831475923365854</v>
+        <v>0.04912212174872113</v>
       </c>
       <c r="AD31" t="n">
         <v>0.6881269433167041</v>
@@ -4235,19 +4235,19 @@
         <v>0.003002730999824887</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.1514510025280846</v>
+        <v>-0.1484664518073479</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.1476017869456593</v>
+        <v>0.1436284313327295</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.1227019127325566</v>
+        <v>-0.1160886644460475</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.1390559283838155</v>
+        <v>-0.1503114689461474</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.03240496841409118</v>
+        <v>0.00837591385332595</v>
       </c>
     </row>
     <row r="32">
@@ -4263,16 +4263,16 @@
         <v>0.03295015558181613</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0843632097106502</v>
+        <v>0.08007122767994836</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.001073226763926525</v>
+        <v>-0.007945162934431186</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07182468346390714</v>
+        <v>0.06051838688585841</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05765369378247829</v>
+        <v>0.04997298960377877</v>
       </c>
       <c r="H32" t="n">
         <v>0.1944732397008409</v>
@@ -4284,10 +4284,10 @@
         <v>-0.08387735642836944</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2177088933345541</v>
+        <v>0.2167512360872801</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2255341812426294</v>
+        <v>0.2266983494827063</v>
       </c>
       <c r="M32" t="n">
         <v>-0.1565083494218037</v>
@@ -4296,13 +4296,13 @@
         <v>-0.09252441832732899</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.2245796735081942</v>
+        <v>-0.2052821062617807</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.09697566414782452</v>
+        <v>-0.08883271402400218</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.3014803137141585</v>
+        <v>-0.2573460553043674</v>
       </c>
       <c r="R32" t="n">
         <v>0.2692675247950936</v>
@@ -4320,7 +4320,7 @@
         <v>0.246530084630679</v>
       </c>
       <c r="W32" t="n">
-        <v>0.006163971522607235</v>
+        <v>-0.01308147950541802</v>
       </c>
       <c r="X32" t="n">
         <v>0.1634028072491838</v>
@@ -4338,7 +4338,7 @@
         <v>0.5525084851151121</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.03267384759903268</v>
+        <v>-0.03452605771498241</v>
       </c>
       <c r="AD32" t="n">
         <v>0.7370316037769507</v>
@@ -4356,19 +4356,19 @@
         <v>-0.009880014847870685</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.0712034424048999</v>
+        <v>-0.07019113506320802</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.06165152574210028</v>
+        <v>-0.05918564515183059</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.001315702547299571</v>
+        <v>0.005713120084232423</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.01858158644651077</v>
+        <v>-0.03408282083733725</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.03189300047729045</v>
+        <v>-0.004168532001278352</v>
       </c>
     </row>
     <row r="33">
@@ -4384,16 +4384,16 @@
         <v>0.05616198657881089</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07362567471653692</v>
+        <v>0.06991747601996672</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.02099825952236134</v>
+        <v>-0.02711440004087012</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1246760319422253</v>
+        <v>0.1111759214855886</v>
       </c>
       <c r="G33" t="n">
-        <v>0.05856342167310739</v>
+        <v>0.05343478797322928</v>
       </c>
       <c r="H33" t="n">
         <v>0.180087748700053</v>
@@ -4405,10 +4405,10 @@
         <v>-0.0546615760471335</v>
       </c>
       <c r="K33" t="n">
-        <v>0.21983081610202</v>
+        <v>0.2189806334906803</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2161275567975152</v>
+        <v>0.2235550565729793</v>
       </c>
       <c r="M33" t="n">
         <v>-0.1766282171404797</v>
@@ -4417,13 +4417,13 @@
         <v>-0.0961510938328643</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.1899924043024699</v>
+        <v>-0.1829445672900349</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.06010359439647176</v>
+        <v>-0.06054585705728616</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.2436411680752137</v>
+        <v>-0.2127048209960673</v>
       </c>
       <c r="R33" t="n">
         <v>0.2360530163582266</v>
@@ -4441,7 +4441,7 @@
         <v>0.2264378879820348</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.04085001499879626</v>
+        <v>-0.06806957715988012</v>
       </c>
       <c r="X33" t="n">
         <v>0.1557541646364166</v>
@@ -4459,7 +4459,7 @@
         <v>0.501748103112942</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.06918710717919123</v>
+        <v>-0.06256241430684921</v>
       </c>
       <c r="AD33" t="n">
         <v>0.6992575747714221</v>
@@ -4477,19 +4477,19 @@
         <v>-0.05288763269564434</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.06166113018559995</v>
+        <v>-0.0611451950377027</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.05942264787087102</v>
+        <v>-0.05653612610688338</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.02886211872951189</v>
+        <v>0.03241919407750853</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.009324791498472391</v>
+        <v>-0.02372594410218401</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.01136554600864927</v>
+        <v>0.04581932104897693</v>
       </c>
     </row>
     <row r="34">
@@ -4505,16 +4505,16 @@
         <v>-0.1804670030622347</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.014911793856841</v>
+        <v>-0.02110083653051632</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.04727260101113926</v>
+        <v>-0.05641117945311341</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.06402858015334047</v>
+        <v>-0.02846033197263121</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01490465596927739</v>
+        <v>0.01355434473537971</v>
       </c>
       <c r="H34" t="n">
         <v>-0.2116886054896172</v>
@@ -4526,10 +4526,10 @@
         <v>0.005251271649771932</v>
       </c>
       <c r="K34" t="n">
-        <v>0.009860795915760247</v>
+        <v>0.01061327966460778</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01587399693792929</v>
+        <v>-0.009870238675361374</v>
       </c>
       <c r="M34" t="n">
         <v>0.0510286854117552</v>
@@ -4538,13 +4538,13 @@
         <v>0.003486093111072676</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1703347643669292</v>
+        <v>0.2290894978090072</v>
       </c>
       <c r="P34" t="n">
-        <v>0.06052424569760188</v>
+        <v>0.07621490561587219</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.09239450980788627</v>
+        <v>0.1437570260888105</v>
       </c>
       <c r="R34" t="n">
         <v>-0.1675310295187097</v>
@@ -4562,7 +4562,7 @@
         <v>-0.1613488778398614</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.04743782672105915</v>
+        <v>-0.02894614355273606</v>
       </c>
       <c r="X34" t="n">
         <v>0.03247128521635469</v>
@@ -4580,7 +4580,7 @@
         <v>0.2976280366672266</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.03227396357478368</v>
+        <v>-0.03041741745842462</v>
       </c>
       <c r="AD34" t="n">
         <v>-0.007425249916527521</v>
@@ -4598,19 +4598,19 @@
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.2324523973527401</v>
+        <v>0.2265378133860182</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-0.1087108083650394</v>
+        <v>-0.09933338419316586</v>
       </c>
       <c r="AK34" t="n">
-        <v>-0.04129854388808389</v>
+        <v>-0.03104360768241682</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.07318782973449996</v>
+        <v>-0.09352175669449525</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.01757234076120981</v>
+        <v>-0.08060746232346858</v>
       </c>
     </row>
     <row r="35">
@@ -4620,118 +4620,118 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.09122175390201313</v>
+        <v>-0.08484240742183938</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.06052092828100717</v>
+        <v>-0.06190062399522441</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0681972214148943</v>
+        <v>0.06881470152137929</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.08139807031418138</v>
+        <v>-0.0733885287754093</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0661143761866599</v>
+        <v>0.02784505313925478</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.03260566627404664</v>
+        <v>-0.03302448878774304</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1752383963733126</v>
+        <v>-0.1702429951088437</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.09698478758265774</v>
+        <v>-0.09216256428026545</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.04040255342109172</v>
+        <v>-0.03858567205224968</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03813344553728248</v>
+        <v>-0.03895475414331239</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.0212890779159672</v>
+        <v>-0.03356186871102722</v>
       </c>
       <c r="M35" t="n">
-        <v>0.01147320186348751</v>
+        <v>0.01094180656881368</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.0327574618089554</v>
+        <v>-0.03146695457714797</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05278542291747129</v>
+        <v>0.08400077205681279</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1119950397335723</v>
+        <v>0.1099839020297817</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1365750767395381</v>
+        <v>0.1504799996820795</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.1911945001313806</v>
+        <v>-0.1855669612761618</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.1905374695487829</v>
+        <v>-0.1858861743209482</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.1295209675592268</v>
+        <v>-0.1264554653918906</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.2002201447242642</v>
+        <v>-0.1948842633346706</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.1787565341617213</v>
+        <v>-0.170776994770234</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.07344427226575594</v>
+        <v>-0.04159488933549275</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.04961671219776224</v>
+        <v>-0.04611701833105515</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.01142005906571321</v>
+        <v>0.01397366050773529</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.1068816273561675</v>
+        <v>-0.1040131820551513</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.1366226559693828</v>
+        <v>-0.1338183402503031</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.06983959254208889</v>
+        <v>0.06849065339056694</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.1222341169794451</v>
+        <v>-0.1119919591087561</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.01409316122927576</v>
+        <v>0.0103967854825519</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.1514510025280846</v>
+        <v>-0.1484664518073479</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.0712034424048999</v>
+        <v>-0.07019113506320802</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.06166113018559995</v>
+        <v>-0.0611451950377027</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.2324523973527401</v>
+        <v>0.2265378133860182</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-0.1718316511874201</v>
+        <v>-0.1649262823727669</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.1031319668917575</v>
+        <v>-0.1042027309016977</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.01596356608292619</v>
+        <v>0.02725736296753237</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.04252061984974782</v>
+        <v>0.002581907862626333</v>
       </c>
     </row>
     <row r="36">
@@ -4741,118 +4741,118 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1627150701953262</v>
+        <v>0.1548307510922242</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0625304406048659</v>
+        <v>-0.06246099591702999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01502787558114161</v>
+        <v>0.01378883235348099</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.103003084696228</v>
+        <v>-0.1041093942764987</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1251391444767959</v>
+        <v>-0.1147404779317038</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.07859417340390126</v>
+        <v>-0.07216711590527908</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1251919142871922</v>
+        <v>0.1202867638719387</v>
       </c>
       <c r="I36" t="n">
-        <v>0.156123524679657</v>
+        <v>0.1465792869191176</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04129710087961907</v>
+        <v>0.04152788268831505</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03647408130117411</v>
+        <v>0.03067869317447792</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1178945907209771</v>
+        <v>0.1063998781326855</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0106415171849012</v>
+        <v>0.009288825802711474</v>
       </c>
       <c r="N36" t="n">
-        <v>0.008376228111177872</v>
+        <v>0.007907600891729346</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.09393211872795122</v>
+        <v>-0.07492660510083043</v>
       </c>
       <c r="P36" t="n">
-        <v>0.01504530731516486</v>
+        <v>0.0178665587082704</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.1999930150571219</v>
+        <v>-0.1938288890453189</v>
       </c>
       <c r="R36" t="n">
-        <v>0.2220714710028329</v>
+        <v>0.2131851614955034</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2310744579748674</v>
+        <v>0.2218990933016167</v>
       </c>
       <c r="T36" t="n">
-        <v>0.206549783567091</v>
+        <v>0.2003850177112176</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2006215124812954</v>
+        <v>0.1891440174168869</v>
       </c>
       <c r="V36" t="n">
-        <v>0.1477219894042046</v>
+        <v>0.1370548888055075</v>
       </c>
       <c r="W36" t="n">
-        <v>0.1019862331108075</v>
+        <v>0.1161808833535688</v>
       </c>
       <c r="X36" t="n">
-        <v>0.09804226397202295</v>
+        <v>0.09054420123134811</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.01597939341233144</v>
+        <v>0.01459935048643615</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.2273766618293648</v>
+        <v>0.2252185624624827</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.1915971443985935</v>
+        <v>0.1789941163618803</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.03388433276083041</v>
+        <v>-0.03240622259132252</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.258176204423206</v>
+        <v>0.2271404550801812</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.03791500647245184</v>
+        <v>-0.0350886258345296</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.1476017869456593</v>
+        <v>0.1436284313327295</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.06165152574210028</v>
+        <v>-0.05918564515183059</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.05942264787087102</v>
+        <v>-0.05653612610688338</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.1087108083650394</v>
+        <v>-0.09933338419316586</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.1718316511874201</v>
+        <v>-0.1649262823727669</v>
       </c>
       <c r="AJ36" t="n">
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.1157639600101156</v>
+        <v>-0.1115784096518001</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.05412184770584932</v>
+        <v>0.04754777625442608</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.03196345306444565</v>
+        <v>-0.01594215252001584</v>
       </c>
     </row>
     <row r="37">
@@ -4862,118 +4862,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.04383903999429569</v>
+        <v>-0.04669591536004186</v>
       </c>
       <c r="C37" t="n">
-        <v>0.04933643333490437</v>
+        <v>0.05126529561964581</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03522436781876354</v>
+        <v>0.03388822699170132</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08332380897952964</v>
+        <v>0.08131643239271596</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1633225378394353</v>
+        <v>0.1374010737681006</v>
       </c>
       <c r="G37" t="n">
-        <v>0.03393762895137785</v>
+        <v>0.03792875946020183</v>
       </c>
       <c r="H37" t="n">
-        <v>0.06603468240498915</v>
+        <v>0.06555470531243922</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.03254281852133409</v>
+        <v>-0.0342765238618274</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.02866247292563552</v>
+        <v>-0.02718709560970321</v>
       </c>
       <c r="K37" t="n">
-        <v>0.05985992870003543</v>
+        <v>0.05637662508521338</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.03026562606806254</v>
+        <v>-0.02167657846621577</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.02503388743247075</v>
+        <v>-0.02610901532063269</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.02519420189809373</v>
+        <v>-0.02502656063954326</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.03196941172687597</v>
+        <v>-0.01257276528809492</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.05402500862980715</v>
+        <v>-0.04497744753174134</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.1118327614878394</v>
+        <v>-0.07132893122846569</v>
       </c>
       <c r="R37" t="n">
-        <v>0.09376647633867986</v>
+        <v>0.09114767049489604</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1020855286408996</v>
+        <v>0.09925432707567487</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07912028713796745</v>
+        <v>0.08228642455195354</v>
       </c>
       <c r="U37" t="n">
-        <v>0.1207274448860888</v>
+        <v>0.1165985744146733</v>
       </c>
       <c r="V37" t="n">
-        <v>0.08352702909726634</v>
+        <v>0.07783981400362308</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.2360717864576095</v>
+        <v>-0.2122130026936639</v>
       </c>
       <c r="X37" t="n">
-        <v>0.03069142533919158</v>
+        <v>0.02841425414292002</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.05634425641252028</v>
+        <v>0.05594955270100413</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.004511913593645942</v>
+        <v>0.005564488750545114</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.1003073853843945</v>
+        <v>0.09915067048322244</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.00396103921222094</v>
+        <v>0.00084453577409378</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.08790868932269284</v>
+        <v>0.07521081750648492</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.07461267644836189</v>
+        <v>-0.06741420290390326</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.1227019127325566</v>
+        <v>-0.1160886644460475</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.001315702547299571</v>
+        <v>0.005713120084232423</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.02886211872951189</v>
+        <v>0.03241919407750853</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.04129854388808389</v>
+        <v>-0.03104360768241682</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.1031319668917575</v>
+        <v>-0.1042027309016977</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0.1157639600101156</v>
+        <v>-0.1115784096518001</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.3213725045417799</v>
+        <v>0.315077152279402</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.06796018483876504</v>
+        <v>-0.06540091708689139</v>
       </c>
     </row>
     <row r="38">
@@ -4983,118 +4983,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.01094470101620679</v>
+        <v>0.02271001079786113</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01609378458120131</v>
+        <v>0.000350193098988409</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05060798604217933</v>
+        <v>0.05195175966304226</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03610061686049243</v>
+        <v>0.04157546475720989</v>
       </c>
       <c r="F38" t="n">
-        <v>0.001336323813537968</v>
+        <v>-0.02787001231212922</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005753641990902556</v>
+        <v>0.008140878375632267</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.005225255157525568</v>
+        <v>-0.006889216304495412</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0160119415029926</v>
+        <v>0.01760323797158125</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.04907419445206011</v>
+        <v>-0.05380690949701126</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.01154456506168584</v>
+        <v>-0.008939013383730335</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.03846968406239749</v>
+        <v>-0.03099691021701918</v>
       </c>
       <c r="M38" t="n">
-        <v>0.07497304633080538</v>
+        <v>0.08300859760573071</v>
       </c>
       <c r="N38" t="n">
-        <v>0.04450979796228239</v>
+        <v>0.04814317277006933</v>
       </c>
       <c r="O38" t="n">
-        <v>0.08802182794324812</v>
+        <v>0.1206405395773167</v>
       </c>
       <c r="P38" t="n">
-        <v>0.02290391387001612</v>
+        <v>0.02757258923106162</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.06095421984208246</v>
+        <v>0.04081703778331965</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.0529204742474713</v>
+        <v>-0.04926556303736935</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.05011621984621317</v>
+        <v>-0.04620970029816943</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.05520368317252184</v>
+        <v>-0.06209343820765205</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.0718097083205487</v>
+        <v>-0.06785579478718096</v>
       </c>
       <c r="V38" t="n">
-        <v>-0.06047380963377873</v>
+        <v>-0.05294457798265444</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.06570141940374311</v>
+        <v>-0.02544664002816167</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.0143453522500506</v>
+        <v>-0.0114700008913392</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.02324241148058295</v>
+        <v>-0.01731025347292364</v>
       </c>
       <c r="Z38" t="n">
-        <v>-0.05416885496615106</v>
+        <v>-0.05722800597492647</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.03697518345647147</v>
+        <v>0.03407429456754927</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.01185035880722155</v>
+        <v>-0.01901783765956438</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.08842910318723335</v>
+        <v>0.07104268120330925</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.0643148034487168</v>
+        <v>-0.06992193156964867</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.1390559283838155</v>
+        <v>-0.1503114689461474</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.01858158644651077</v>
+        <v>-0.03408282083733725</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.009324791498472391</v>
+        <v>-0.02372594410218401</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.07318782973449996</v>
+        <v>-0.09352175669449525</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.01596356608292619</v>
+        <v>0.02725736296753237</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.05412184770584932</v>
+        <v>0.04754777625442608</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.3213725045417799</v>
+        <v>0.315077152279402</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.0249258273643574</v>
+        <v>0.01056399676449412</v>
       </c>
     </row>
     <row r="39">
@@ -5104,115 +5104,115 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0244739038608021</v>
+        <v>-0.004955794830383358</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1386092172685593</v>
+        <v>0.1287119571779566</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.134523572250927</v>
+        <v>-0.13337518964588</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.04547968881871365</v>
+        <v>-0.02630918784592106</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.05636340380248044</v>
+        <v>-0.04658099815293717</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.02507077126245716</v>
+        <v>-0.03227057279931734</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1074469823751557</v>
+        <v>-0.06430633081024528</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.03707083945259072</v>
+        <v>-0.03184953565680757</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3577912521557281</v>
+        <v>0.1634438845988278</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1164253945870401</v>
+        <v>0.09282759802525414</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.1285314205501864</v>
+        <v>-0.08966085872312413</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05248787567619771</v>
+        <v>0.02348216410198609</v>
       </c>
       <c r="N39" t="n">
-        <v>0.05022381199695129</v>
+        <v>0.02892413519219711</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.01489742231702872</v>
+        <v>-0.05536307153215934</v>
       </c>
       <c r="P39" t="n">
-        <v>0.02475817364149503</v>
+        <v>0.005260498615053966</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2164468210718996</v>
+        <v>0.1337823610655039</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.1873846917596958</v>
+        <v>-0.1369379216734689</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.1964282141661401</v>
+        <v>-0.1442687416081952</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.1806767078732945</v>
+        <v>-0.1324375143282568</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.1935109417640029</v>
+        <v>-0.1393279899529387</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.1948893492995449</v>
+        <v>-0.1346534173060699</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.01432306653619482</v>
+        <v>-0.0264322039451852</v>
       </c>
       <c r="X39" t="n">
-        <v>0.07689488514718229</v>
+        <v>0.05998910641119317</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.1315621616348011</v>
+        <v>-0.1351918422274742</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.05555018540259088</v>
+        <v>0.05244120467817286</v>
       </c>
       <c r="AA39" t="n">
-        <v>-0.0009015844660605205</v>
+        <v>0.01088459472383434</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.0008230545258206735</v>
+        <v>0.01634847735115262</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.02150768262079008</v>
+        <v>-0.01128786384927623</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.008233524447443708</v>
+        <v>0.04182420721745185</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.03240496841409118</v>
+        <v>0.00837591385332595</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.03189300047729045</v>
+        <v>-0.004168532001278352</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01136554600864927</v>
+        <v>0.04581932104897693</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.01757234076120981</v>
+        <v>-0.08060746232346858</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.04252061984974782</v>
+        <v>0.002581907862626333</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-0.03196345306444565</v>
+        <v>-0.01594215252001584</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.06796018483876504</v>
+        <v>-0.06540091708689139</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.0249258273643574</v>
+        <v>0.01056399676449412</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
